--- a/Tests Data/Kyocera KC85TS/Single diode model/G = 400 W.m^-2 and T = 25ºC/R+L load/Single-diode emulator - R+L - Kyocera KC85TS (ref = STC, G = 400 and T = 25).xlsx
+++ b/Tests Data/Kyocera KC85TS/Single diode model/G = 400 W.m^-2 and T = 25ºC/R+L load/Single-diode emulator - R+L - Kyocera KC85TS (ref = STC, G = 400 and T = 25).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Stage_GeePs\Test Data - new\Kyocera KC85TS\Single diode model\G = 400 W.m^-2 and T = 25ºC\R+L load\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Stage_GeePs\PV-emulator\Tests Data\Kyocera KC85TS\Single diode model\G = 400 W.m^-2 and T = 25ºC\R+L load\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B3A28B-72A6-4996-BD8C-895CF326FA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B0F466-5F60-4F13-9522-F99B2FC531A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{217CCB4B-160F-4504-987F-9C10DFEEC66E}"/>
+    <workbookView xWindow="34785" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{217CCB4B-160F-4504-987F-9C10DFEEC66E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -537,57 +537,57 @@
         <v>60</v>
       </c>
       <c r="B2">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="C2">
         <f>A2*B2</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>5.08</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <f>D2*E2</f>
-        <v>10.8712</v>
+        <v>8</v>
       </c>
       <c r="G2">
         <f>D2/E2</f>
-        <v>2.3738317757009346</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>22.491859000000002</v>
+        <v>22.491726</v>
       </c>
       <c r="I2">
-        <v>8.8391520000000003</v>
+        <v>11.401453</v>
       </c>
       <c r="J2">
-        <v>5.4229810000000001</v>
+        <v>4.2121060000000003</v>
       </c>
       <c r="K2">
-        <v>2.1311960000000001</v>
+        <v>2.1351909999999998</v>
       </c>
       <c r="L2">
         <f>J2/K2</f>
-        <v>2.5445716865084207</v>
+        <v>1.9727068913272867</v>
       </c>
       <c r="M2">
         <f>ABS(J2-D2)/D2*100</f>
-        <v>6.7515944881889762</v>
+        <v>5.3026500000000087</v>
       </c>
       <c r="N2">
         <f>ABS(K2-E2)/E2*100</f>
-        <v>0.41140186915888005</v>
+        <v>6.759549999999992</v>
       </c>
       <c r="O2">
-        <f t="shared" ref="O2:O19" si="0">(ABS(L2-G2)/G2)*100</f>
-        <v>7.1925867938586654</v>
+        <f t="shared" ref="O2:O17" si="0">(ABS(L2-G2)/G2)*100</f>
+        <v>1.3646554336356642</v>
       </c>
       <c r="P2">
-        <f t="shared" ref="P2:P19" si="1">(F2/C2)*100</f>
-        <v>60.395555555555561</v>
+        <f t="shared" ref="P2:P17" si="1">(F2/C2)*100</f>
+        <v>53.333333333333336</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -595,57 +595,57 @@
         <v>60</v>
       </c>
       <c r="B3">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="C3">
         <f>A3*B3</f>
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
       <c r="D3">
-        <v>9.83</v>
+        <v>9.99</v>
       </c>
       <c r="E3">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="F3">
         <f>D3*E3</f>
-        <v>20.544699999999999</v>
+        <v>20.1798</v>
       </c>
       <c r="G3">
         <f>D3/E3</f>
-        <v>4.7033492822966512</v>
+        <v>4.9455445544554459</v>
       </c>
       <c r="H3">
-        <v>22.785050999999999</v>
+        <v>22.784645000000001</v>
       </c>
       <c r="I3">
-        <v>4.6931900000000004</v>
+        <v>4.7635430000000003</v>
       </c>
       <c r="J3">
-        <v>10.325286999999999</v>
+        <v>10.206792</v>
       </c>
       <c r="K3">
-        <v>2.1267680000000002</v>
+        <v>2.133915</v>
       </c>
       <c r="L3">
         <f>J3/K3</f>
-        <v>4.8549192953815359</v>
+        <v>4.7831295998200494</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M19" si="2">ABS(J3-D3)/D3*100</f>
-        <v>5.0385249237029441</v>
+        <f t="shared" ref="M3:M17" si="2">ABS(J3-D3)/D3*100</f>
+        <v>2.1700900900900888</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N19" si="3">ABS(K3-E3)/E3*100</f>
-        <v>1.7592344497607826</v>
+        <f t="shared" ref="N3:N17" si="3">ABS(K3-E3)/E3*100</f>
+        <v>5.6393564356435641</v>
       </c>
       <c r="O3">
         <f t="shared" si="0"/>
-        <v>3.2225974297803566</v>
+        <v>3.2840661497847949</v>
       </c>
       <c r="P3">
         <f t="shared" si="1"/>
-        <v>74.437318840579707</v>
+        <v>76.438636363636363</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -653,57 +653,57 @@
         <v>60</v>
       </c>
       <c r="B4">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="C4">
         <f t="shared" ref="C4:C16" si="4">A2*B4</f>
-        <v>32.400000000000006</v>
+        <v>31.200000000000003</v>
       </c>
       <c r="D4">
-        <v>11.96</v>
+        <v>12.45</v>
       </c>
       <c r="E4">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="F4">
         <f>D4*E4</f>
-        <v>24.996400000000001</v>
+        <v>25.398</v>
       </c>
       <c r="G4">
         <f>D4/E4</f>
-        <v>5.722488038277513</v>
+        <v>6.1029411764705879</v>
       </c>
       <c r="H4">
-        <v>22.491726</v>
+        <v>22.494654000000001</v>
       </c>
       <c r="I4">
-        <v>3.834816</v>
+        <v>3.7908819999999999</v>
       </c>
       <c r="J4">
-        <v>12.457455</v>
+        <v>12.650107999999999</v>
       </c>
       <c r="K4">
-        <v>2.123983</v>
+        <v>2.1318429999999999</v>
       </c>
       <c r="L4">
         <f>J4/K4</f>
-        <v>5.8651387511105311</v>
+        <v>5.9338834989255771</v>
       </c>
       <c r="M4">
         <f t="shared" si="2"/>
-        <v>4.1593227424749042</v>
+        <v>1.6072931726907644</v>
       </c>
       <c r="N4">
         <f t="shared" si="3"/>
-        <v>1.6259808612440239</v>
+        <v>4.5021078431372503</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>2.4928092794398649</v>
+        <v>2.7701017043519838</v>
       </c>
       <c r="P4">
         <f t="shared" si="1"/>
-        <v>77.149382716049374</v>
+        <v>81.403846153846146</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -718,50 +718,50 @@
         <v>34.799999999999997</v>
       </c>
       <c r="D5">
-        <v>13.25</v>
+        <v>13.63</v>
       </c>
       <c r="E5" s="3">
-        <v>2.0699999999999998</v>
+        <v>2.09</v>
       </c>
       <c r="F5">
         <f>D5*E5</f>
-        <v>27.427499999999998</v>
+        <v>28.486699999999999</v>
       </c>
       <c r="G5">
         <f>D5/E5</f>
-        <v>6.4009661835748801</v>
+        <v>6.5215311004784695</v>
       </c>
       <c r="H5">
-        <v>22.494526</v>
+        <v>22.494001000000001</v>
       </c>
       <c r="I5">
-        <v>3.4821040000000001</v>
+        <v>3.46787</v>
       </c>
       <c r="J5">
-        <v>13.701180000000001</v>
+        <v>13.811143</v>
       </c>
       <c r="K5">
-        <v>2.1209129999999998</v>
+        <v>2.1292450000000001</v>
       </c>
       <c r="L5">
         <f t="shared" ref="L5:L15" si="5">J5/K5</f>
-        <v>6.4600386720247371</v>
+        <v>6.4864038661591312</v>
       </c>
       <c r="M5">
         <f t="shared" si="2"/>
-        <v>3.405132075471704</v>
+        <v>1.3290022010271365</v>
       </c>
       <c r="N5">
         <f t="shared" si="3"/>
-        <v>2.4595652173913041</v>
+        <v>1.8777511961722584</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>0.92286831012229442</v>
+        <v>0.53863477422903161</v>
       </c>
       <c r="P5">
         <f t="shared" si="1"/>
-        <v>78.814655172413794</v>
+        <v>81.858333333333334</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -769,57 +769,57 @@
         <v>60</v>
       </c>
       <c r="B6">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="C6">
         <f t="shared" si="4"/>
-        <v>37.799999999999997</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="D6">
-        <v>14.66</v>
+        <v>14.82</v>
       </c>
       <c r="E6" s="3">
-        <v>2.06</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F6">
         <f>D6*E6</f>
-        <v>30.1996</v>
+        <v>30.084599999999998</v>
       </c>
       <c r="G6">
         <f>D6/E6</f>
-        <v>7.116504854368932</v>
+        <v>7.3004926108374395</v>
       </c>
       <c r="H6">
-        <v>22.493938</v>
+        <v>22.494892</v>
       </c>
       <c r="I6">
-        <v>3.150763</v>
+        <v>3.1853799999999999</v>
       </c>
       <c r="J6">
-        <v>15.073689</v>
+        <v>14.974235999999999</v>
       </c>
       <c r="K6">
-        <v>2.1113960000000001</v>
+        <v>2.1204200000000002</v>
       </c>
       <c r="L6">
         <f t="shared" ref="L6" si="6">J6/K6</f>
-        <v>7.1392050567491836</v>
+        <v>7.061919808339856</v>
       </c>
       <c r="M6">
         <f t="shared" si="2"/>
-        <v>2.8218894952251006</v>
+        <v>1.0407287449392655</v>
       </c>
       <c r="N6">
         <f t="shared" si="3"/>
-        <v>2.4949514563106794</v>
+        <v>4.4541871921182459</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>0.31897965145510448</v>
+        <v>3.2679000612017166</v>
       </c>
       <c r="P6">
         <f t="shared" si="1"/>
-        <v>79.893121693121699</v>
+        <v>80.872580645161278</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -827,57 +827,57 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="C7">
         <f t="shared" si="4"/>
-        <v>38.4</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="D7">
-        <v>15.27</v>
+        <v>15.5</v>
       </c>
       <c r="E7">
-        <v>2.0499999999999998</v>
+        <v>2.04</v>
       </c>
       <c r="F7">
         <f t="shared" ref="F7" si="7">D7*E7</f>
-        <v>31.303499999999996</v>
+        <v>31.62</v>
       </c>
       <c r="G7">
         <f t="shared" ref="G7" si="8">D7/E7</f>
-        <v>7.4487804878048784</v>
+        <v>7.5980392156862742</v>
       </c>
       <c r="H7">
-        <v>22.496943000000002</v>
+        <v>22.493297999999999</v>
       </c>
       <c r="I7">
-        <v>3.016575</v>
+        <v>3.0357440000000002</v>
       </c>
       <c r="J7">
-        <v>15.675177</v>
+        <v>15.629344</v>
       </c>
       <c r="K7">
-        <v>2.1018560000000002</v>
+        <v>2.1093700000000002</v>
       </c>
       <c r="L7">
         <f t="shared" si="5"/>
-        <v>7.4577787441194818</v>
+        <v>7.4094843484073438</v>
       </c>
       <c r="M7">
         <f t="shared" si="2"/>
-        <v>2.653418467583498</v>
+        <v>0.83447741935483655</v>
       </c>
       <c r="N7">
         <f t="shared" si="3"/>
-        <v>2.5295609756097734</v>
+        <v>3.4004901960784388</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.12080173834274348</v>
+        <v>2.481625349993664</v>
       </c>
       <c r="P7">
         <f t="shared" si="1"/>
-        <v>81.519531249999986</v>
+        <v>83.650793650793659</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -885,57 +885,57 @@
         <v>60</v>
       </c>
       <c r="B8">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="C8">
         <f t="shared" si="4"/>
-        <v>39</v>
+        <v>39.6</v>
       </c>
       <c r="D8">
-        <v>15.67</v>
+        <v>16.05</v>
       </c>
       <c r="E8">
-        <v>2.0299999999999998</v>
+        <v>2.04</v>
       </c>
       <c r="F8">
         <f>D8*E8</f>
-        <v>31.810099999999998</v>
+        <v>32.742000000000004</v>
       </c>
       <c r="G8">
         <f t="shared" ref="G8:G12" si="9">D8/E8</f>
-        <v>7.7192118226600996</v>
+        <v>7.8676470588235299</v>
       </c>
       <c r="H8">
-        <v>22.492146999999999</v>
+        <v>22.49297</v>
       </c>
       <c r="I8">
-        <v>2.923689</v>
+        <v>2.9085359999999998</v>
       </c>
       <c r="J8">
-        <v>16.085083000000001</v>
+        <v>16.181227</v>
       </c>
       <c r="K8">
-        <v>2.0908540000000002</v>
+        <v>2.0923729999999998</v>
       </c>
       <c r="L8">
         <f t="shared" si="5"/>
-        <v>7.6930684782390353</v>
+        <v>7.733433283644934</v>
       </c>
       <c r="M8">
         <f t="shared" si="2"/>
-        <v>2.6489023611997506</v>
+        <v>0.8176137071651034</v>
       </c>
       <c r="N8">
         <f t="shared" si="3"/>
-        <v>2.9977339901478035</v>
+        <v>2.5673039215686164</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>0.33867893538456062</v>
+        <v>1.7058947125503776</v>
       </c>
       <c r="P8">
         <f t="shared" si="1"/>
-        <v>81.564358974358981</v>
+        <v>82.681818181818187</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -943,57 +943,57 @@
         <v>60</v>
       </c>
       <c r="B9">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="C9">
         <f t="shared" si="4"/>
-        <v>39.6</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="D9">
-        <v>16.04</v>
+        <v>16.45</v>
       </c>
       <c r="E9">
         <v>2.0299999999999998</v>
       </c>
       <c r="F9">
         <f>D9*E9</f>
-        <v>32.561199999999992</v>
+        <v>33.393499999999996</v>
       </c>
       <c r="G9">
         <f t="shared" ref="G9" si="10">D9/E9</f>
-        <v>7.9014778325123158</v>
+        <v>8.1034482758620694</v>
       </c>
       <c r="H9">
-        <v>22.493511000000002</v>
+        <v>22.495255</v>
       </c>
       <c r="I9">
-        <v>2.841831</v>
+        <v>2.8102299999999998</v>
       </c>
       <c r="J9">
-        <v>16.439855999999999</v>
+        <v>16.588014999999999</v>
       </c>
       <c r="K9">
-        <v>2.0770119999999999</v>
+        <v>2.0722659999999999</v>
       </c>
       <c r="L9">
         <f t="shared" ref="L9" si="11">J9/K9</f>
-        <v>7.9151473366547718</v>
+        <v>8.0047711056399127</v>
       </c>
       <c r="M9">
         <f t="shared" si="2"/>
-        <v>2.4928678304239389</v>
+        <v>0.83899696048631811</v>
       </c>
       <c r="N9">
         <f t="shared" si="3"/>
-        <v>2.31586206896552</v>
+        <v>2.0820689655172484</v>
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>0.17299933546873783</v>
+        <v>1.2177182708266148</v>
       </c>
       <c r="P9">
         <f t="shared" si="1"/>
-        <v>82.2252525252525</v>
+        <v>83.068407960198982</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1008,50 +1008,50 @@
         <v>40.200000000000003</v>
       </c>
       <c r="D10">
-        <v>16.579999999999998</v>
+        <v>17.010000000000002</v>
       </c>
       <c r="E10">
         <v>1.98</v>
       </c>
       <c r="F10">
         <f>D10*E10</f>
-        <v>32.828399999999995</v>
+        <v>33.6798</v>
       </c>
       <c r="G10">
         <f>D10/E10</f>
-        <v>8.3737373737373737</v>
+        <v>8.5909090909090917</v>
       </c>
       <c r="H10">
-        <v>22.493787999999999</v>
+        <v>22.493977000000001</v>
       </c>
       <c r="I10">
-        <v>2.7113100000000001</v>
+        <v>2.6707040000000002</v>
       </c>
       <c r="J10">
-        <v>16.966587000000001</v>
+        <v>17.113244999999999</v>
       </c>
       <c r="K10">
-        <v>2.0450840000000001</v>
+        <v>2.0318510000000001</v>
       </c>
       <c r="L10">
         <f t="shared" si="5"/>
-        <v>8.2962787836587637</v>
+        <v>8.4224901333808422</v>
       </c>
       <c r="M10">
         <f t="shared" si="2"/>
-        <v>2.3316465621230535</v>
+        <v>0.60696649029980931</v>
       </c>
       <c r="N10">
         <f t="shared" si="3"/>
-        <v>3.2870707070707139</v>
+        <v>2.6187373737373782</v>
       </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>0.92501814448520991</v>
+        <v>1.9604323098526399</v>
       </c>
       <c r="P10">
         <f t="shared" si="1"/>
-        <v>81.662686567164158</v>
+        <v>83.780597014925377</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1059,57 +1059,57 @@
         <v>60</v>
       </c>
       <c r="B11">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="C11">
         <f t="shared" si="4"/>
-        <v>40.200000000000003</v>
+        <v>39.6</v>
       </c>
       <c r="D11">
-        <v>16.97</v>
+        <v>17.47</v>
       </c>
       <c r="E11">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="F11">
         <f>D11*E11</f>
-        <v>33.261199999999995</v>
+        <v>33.192999999999998</v>
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>8.658163265306122</v>
+        <v>9.1947368421052627</v>
       </c>
       <c r="H11">
-        <v>22.492806999999999</v>
+        <v>22.493220999999998</v>
       </c>
       <c r="I11">
-        <v>2.604371</v>
+        <v>2.5266500000000001</v>
       </c>
       <c r="J11">
-        <v>17.350944999999999</v>
+        <v>17.581903000000001</v>
       </c>
       <c r="K11">
-        <v>2.0090110000000001</v>
+        <v>1.9749650000000001</v>
       </c>
       <c r="L11">
         <f t="shared" si="5"/>
-        <v>8.6365604767719031</v>
+        <v>8.9023871309111797</v>
       </c>
       <c r="M11">
         <f t="shared" si="2"/>
-        <v>2.2448143783146763</v>
+        <v>0.64054378935318634</v>
       </c>
       <c r="N11">
         <f t="shared" si="3"/>
-        <v>2.500561224489803</v>
+        <v>3.9455263157894827</v>
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>0.24950775207465592</v>
+        <v>3.1795332070335296</v>
       </c>
       <c r="P11">
         <f t="shared" si="1"/>
-        <v>82.739303482587047</v>
+        <v>83.820707070707059</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1117,57 +1117,57 @@
         <v>60</v>
       </c>
       <c r="B12">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="C12">
         <f t="shared" si="4"/>
-        <v>39.6</v>
+        <v>38.4</v>
       </c>
       <c r="D12">
-        <v>17.48</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="E12">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="F12">
         <f>D12*E12</f>
-        <v>32.338000000000001</v>
+        <v>32.381999999999998</v>
       </c>
       <c r="G12">
         <f t="shared" si="9"/>
-        <v>9.4486486486486481</v>
+        <v>9.9944444444444436</v>
       </c>
       <c r="H12">
-        <v>22.494133000000001</v>
+        <v>22.494623000000001</v>
       </c>
       <c r="I12">
-        <v>2.4527999999999999</v>
+        <v>2.3407809999999998</v>
       </c>
       <c r="J12">
-        <v>17.817668999999999</v>
+        <v>18.077916999999999</v>
       </c>
       <c r="K12">
-        <v>1.9428700000000001</v>
+        <v>1.881181</v>
       </c>
       <c r="L12">
         <f t="shared" si="5"/>
-        <v>9.1707983550108843</v>
+        <v>9.6098764552693225</v>
       </c>
       <c r="M12">
         <f t="shared" si="2"/>
-        <v>1.9317448512585711</v>
+        <v>0.48869927737632529</v>
       </c>
       <c r="N12">
         <f t="shared" si="3"/>
-        <v>5.0200000000000005</v>
+        <v>4.5100555555555522</v>
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>2.940635258752077</v>
+        <v>3.8478175681779763</v>
       </c>
       <c r="P12">
         <f t="shared" si="1"/>
-        <v>81.661616161616152</v>
+        <v>84.328125</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1175,57 +1175,57 @@
         <v>60</v>
       </c>
       <c r="B13">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="C13">
         <f t="shared" si="4"/>
-        <v>39</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="D13">
-        <v>17.95</v>
+        <v>18.34</v>
       </c>
       <c r="E13">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="F13">
         <f t="shared" ref="F13:F14" si="12">D13*E13</f>
-        <v>31.951000000000001</v>
+        <v>31.728200000000001</v>
       </c>
       <c r="G13">
         <f>D13/E13</f>
-        <v>10.084269662921347</v>
+        <v>10.601156069364162</v>
       </c>
       <c r="H13">
-        <v>22.494323999999999</v>
+        <v>22.493725000000001</v>
       </c>
       <c r="I13">
-        <v>2.2673649999999999</v>
+        <v>2.1897139999999999</v>
       </c>
       <c r="J13">
-        <v>18.280349999999999</v>
+        <v>18.393583</v>
       </c>
       <c r="K13">
-        <v>1.842608</v>
+        <v>1.7905740000000001</v>
       </c>
       <c r="L13">
         <f t="shared" si="5"/>
-        <v>9.9209110130857994</v>
+        <v>10.272450621979321</v>
       </c>
       <c r="M13">
         <f t="shared" si="2"/>
-        <v>1.8403899721448427</v>
+        <v>0.29216466739367347</v>
       </c>
       <c r="N13">
         <f t="shared" si="3"/>
-        <v>3.5173033707865167</v>
+        <v>3.5013872832370017</v>
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>1.6199353577006963</v>
+        <v>3.1006566192790386</v>
       </c>
       <c r="P13">
         <f t="shared" si="1"/>
-        <v>81.925641025641028</v>
+        <v>83.937037037037044</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1233,57 +1233,57 @@
         <v>60</v>
       </c>
       <c r="B14">
-        <v>0.61</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="C14">
         <f t="shared" si="4"/>
-        <v>36.6</v>
+        <v>34.199999999999996</v>
       </c>
       <c r="D14">
-        <v>18.41</v>
+        <v>18.78</v>
       </c>
       <c r="E14">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="F14">
         <f t="shared" si="12"/>
-        <v>30.192399999999999</v>
+        <v>28.921200000000002</v>
       </c>
       <c r="G14">
         <f>D14/E14</f>
-        <v>11.225609756097562</v>
+        <v>12.194805194805195</v>
       </c>
       <c r="H14">
-        <v>22.494551000000001</v>
+        <v>22.785146999999998</v>
       </c>
       <c r="I14">
-        <v>2.0613299999999999</v>
+        <v>1.989317</v>
       </c>
       <c r="J14">
-        <v>18.678190000000001</v>
+        <v>18.813585</v>
       </c>
       <c r="K14">
-        <v>1.711611</v>
+        <v>1.6425700000000001</v>
       </c>
       <c r="L14">
         <f t="shared" si="5"/>
-        <v>10.912637275642656</v>
+        <v>11.453749307487655</v>
       </c>
       <c r="M14">
         <f t="shared" si="2"/>
-        <v>1.4567626290059783</v>
+        <v>0.17883386581468924</v>
       </c>
       <c r="N14">
         <f t="shared" si="3"/>
-        <v>4.3665243902439084</v>
+        <v>6.6603896103896139</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>2.7880220963935161</v>
+        <v>6.0768161153834459</v>
       </c>
       <c r="P14">
         <f t="shared" si="1"/>
-        <v>82.49289617486339</v>
+        <v>84.564912280701776</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1291,57 +1291,57 @@
         <v>60</v>
       </c>
       <c r="B15">
-        <v>0.55000000000000004</v>
+        <v>0.51</v>
       </c>
       <c r="C15">
         <f t="shared" si="4"/>
-        <v>33</v>
+        <v>30.6</v>
       </c>
       <c r="D15">
-        <v>18.84</v>
+        <v>19.13</v>
       </c>
       <c r="E15">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="F15">
         <f t="shared" ref="F15" si="13">D15*E15</f>
-        <v>27.317999999999998</v>
+        <v>25.6342</v>
       </c>
       <c r="G15">
         <f>D15/E15</f>
-        <v>12.993103448275862</v>
+        <v>14.276119402985072</v>
       </c>
       <c r="H15">
-        <v>22.500011000000001</v>
+        <v>22.501472</v>
       </c>
       <c r="I15">
-        <v>1.8166580000000001</v>
+        <v>1.7104680000000001</v>
       </c>
       <c r="J15">
-        <v>19.048414000000001</v>
+        <v>19.156638999999998</v>
       </c>
       <c r="K15">
-        <v>1.5379750000000001</v>
+        <v>1.456207</v>
       </c>
       <c r="L15">
         <f t="shared" si="5"/>
-        <v>12.385385978315643</v>
+        <v>13.155162006500449</v>
       </c>
       <c r="M15">
         <f t="shared" si="2"/>
-        <v>1.1062314225053143</v>
+        <v>0.13925248301097445</v>
       </c>
       <c r="N15">
         <f t="shared" si="3"/>
-        <v>6.0672413793103539</v>
+        <v>8.6721641791044739</v>
       </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>4.6772310586110288</v>
+        <v>7.8519754902738939</v>
       </c>
       <c r="P15">
         <f t="shared" si="1"/>
-        <v>82.781818181818181</v>
+        <v>83.7718954248366</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1349,57 +1349,57 @@
         <v>60</v>
       </c>
       <c r="B16">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="C16">
         <f t="shared" si="4"/>
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="D16">
-        <v>19.28</v>
+        <v>19.46</v>
       </c>
       <c r="E16">
-        <v>1.18</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F16">
         <f>D16*E16</f>
-        <v>22.750399999999999</v>
+        <v>22.1844</v>
       </c>
       <c r="G16">
-        <f t="shared" ref="G16:G19" si="14">D16/E16</f>
-        <v>16.33898305084746</v>
+        <f t="shared" ref="G16:G17" si="14">D16/E16</f>
+        <v>17.070175438596493</v>
       </c>
       <c r="H16">
-        <v>22.502753999999999</v>
+        <v>22.504978000000001</v>
       </c>
       <c r="I16">
-        <v>1.5469059999999999</v>
+        <v>1.49112</v>
       </c>
       <c r="J16">
-        <v>19.429449000000002</v>
+        <v>19.463346000000001</v>
       </c>
       <c r="K16">
-        <v>1.3356380000000001</v>
+        <v>1.28959</v>
       </c>
       <c r="L16">
-        <f t="shared" ref="L16:L19" si="15">J16/K16</f>
-        <v>14.546942360130515</v>
+        <f t="shared" ref="L16:L17" si="15">J16/K16</f>
+        <v>15.092662008855529</v>
       </c>
       <c r="M16">
         <f t="shared" si="2"/>
-        <v>0.77515041493776238</v>
+        <v>1.7194244604319193E-2</v>
       </c>
       <c r="N16">
         <f t="shared" si="3"/>
-        <v>13.189661016949167</v>
+        <v>13.121929824561414</v>
       </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>10.967883895466777</v>
+        <v>11.584611047814489</v>
       </c>
       <c r="P16">
         <f t="shared" si="1"/>
-        <v>80.675177304964535</v>
+        <v>80.37826086956521</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1407,57 +1407,57 @@
         <v>60</v>
       </c>
       <c r="B17">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="C17">
-        <f t="shared" ref="C17:C19" si="16">A15*B17</f>
-        <v>19.8</v>
+        <f t="shared" ref="C17" si="16">A15*B17</f>
+        <v>18.600000000000001</v>
       </c>
       <c r="D17">
-        <v>19.739999999999998</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="E17">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="F17">
-        <f t="shared" ref="F17:F19" si="17">D17*E17</f>
-        <v>14.607599999999998</v>
+        <f t="shared" ref="F17" si="17">D17*E17</f>
+        <v>13.498000000000001</v>
       </c>
       <c r="G17">
         <f t="shared" si="14"/>
-        <v>26.675675675675674</v>
+        <v>29.191176470588236</v>
       </c>
       <c r="H17">
-        <v>22.785136999999999</v>
+        <v>22.512096</v>
       </c>
       <c r="I17">
-        <v>1.0936870000000001</v>
+        <v>1.0006889999999999</v>
       </c>
       <c r="J17">
-        <v>19.783799999999999</v>
+        <v>19.813057000000001</v>
       </c>
       <c r="K17">
-        <v>0.94962299999999999</v>
+        <v>0.88071299999999997</v>
       </c>
       <c r="L17">
         <f t="shared" si="15"/>
-        <v>20.833320170214915</v>
+        <v>22.496610132926392</v>
       </c>
       <c r="M17">
         <f t="shared" si="2"/>
-        <v>0.22188449848024797</v>
+        <v>0.18611083123426111</v>
       </c>
       <c r="N17">
         <f t="shared" si="3"/>
-        <v>28.327432432432431</v>
+        <v>29.516617647058808</v>
       </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>21.901434012365563</v>
+        <v>22.933527000554427</v>
       </c>
       <c r="P17">
         <f t="shared" si="1"/>
-        <v>73.775757575757567</v>
+        <v>72.569892473118287</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1465,57 +1465,57 @@
         <v>60</v>
       </c>
       <c r="B18">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="C18">
         <f t="shared" ref="C18" si="18">A16*B18</f>
-        <v>13.8</v>
+        <v>9.6</v>
       </c>
       <c r="D18">
-        <v>20.09</v>
+        <v>20.29</v>
       </c>
       <c r="E18">
-        <v>0.39</v>
+        <v>0.18</v>
       </c>
       <c r="F18">
         <f t="shared" ref="F18" si="19">D18*E18</f>
-        <v>7.8351000000000006</v>
+        <v>3.6521999999999997</v>
       </c>
       <c r="G18">
         <f t="shared" ref="G18" si="20">D18/E18</f>
-        <v>51.512820512820511</v>
+        <v>112.72222222222223</v>
       </c>
       <c r="H18">
-        <v>22.514206000000001</v>
+        <v>22.518711</v>
       </c>
       <c r="I18">
-        <v>0.72595399999999999</v>
+        <v>0.457511</v>
       </c>
       <c r="J18">
-        <v>20.036784999999998</v>
+        <v>20.199618999999998</v>
       </c>
       <c r="K18">
-        <v>0.64607099999999995</v>
+        <v>0.41039399999999998</v>
       </c>
       <c r="L18">
         <f t="shared" ref="L18" si="21">J18/K18</f>
-        <v>31.013286465419434</v>
+        <v>49.220064133491228</v>
       </c>
       <c r="M18">
         <f t="shared" ref="M18" si="22">ABS(J18-D18)/D18*100</f>
-        <v>0.26488302638129202</v>
+        <v>0.44544603252834264</v>
       </c>
       <c r="N18">
         <f t="shared" ref="N18" si="23">ABS(K18-E18)/E18*100</f>
-        <v>65.659230769230746</v>
+        <v>127.99666666666667</v>
       </c>
       <c r="O18">
         <f t="shared" ref="O18" si="24">(ABS(L18-G18)/G18)*100</f>
-        <v>39.795013830196218</v>
+        <v>56.335083568120162</v>
       </c>
       <c r="P18">
         <f t="shared" ref="P18" si="25">(F18/C18)*100</f>
-        <v>56.776086956521745</v>
+        <v>38.043749999999996</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1530,50 +1530,50 @@
         <v>7.1999999999999993</v>
       </c>
       <c r="D19">
-        <v>20.48</v>
+        <v>20.41</v>
       </c>
       <c r="E19">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F19">
         <f t="shared" ref="F19" si="27">D19*E19</f>
-        <v>0.81920000000000004</v>
+        <v>1.0205</v>
       </c>
       <c r="G19">
         <f t="shared" ref="G19" si="28">D19/E19</f>
-        <v>512</v>
+        <v>408.2</v>
       </c>
       <c r="H19">
-        <v>22.517738000000001</v>
+        <v>22.517979</v>
       </c>
       <c r="I19">
-        <v>0.31557099999999999</v>
+        <v>0.306336</v>
       </c>
       <c r="J19">
-        <v>20.337689999999998</v>
+        <v>20.309837000000002</v>
       </c>
       <c r="K19">
-        <v>0.28501900000000002</v>
+        <v>0.27629700000000001</v>
       </c>
       <c r="L19">
         <f t="shared" ref="L19" si="29">J19/K19</f>
-        <v>71.35555875222353</v>
+        <v>73.507265732165024</v>
       </c>
       <c r="M19">
         <f t="shared" ref="M19" si="30">ABS(J19-D19)/D19*100</f>
-        <v>0.6948730468750095</v>
+        <v>0.49075453209210407</v>
       </c>
       <c r="N19">
         <f t="shared" ref="N19" si="31">ABS(K19-E19)/E19*100</f>
-        <v>612.54750000000001</v>
+        <v>452.59400000000005</v>
       </c>
       <c r="O19">
         <f t="shared" ref="O19" si="32">(ABS(L19-G19)/G19)*100</f>
-        <v>86.063367431206345</v>
+        <v>81.992340584966911</v>
       </c>
       <c r="P19">
         <f t="shared" ref="P19" si="33">(F19/C19)*100</f>
-        <v>11.37777777777778</v>
+        <v>14.173611111111112</v>
       </c>
     </row>
   </sheetData>
